--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -659,7 +659,6 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>提供人口居住空间</t>
@@ -709,7 +708,6 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>生产食物资源</t>
@@ -764,7 +762,6 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>标准的茅草屋外壳，可自由调节宽度</t>
@@ -814,7 +811,6 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>训练战斗单位</t>
@@ -869,7 +865,6 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>进行资源交易</t>
@@ -924,7 +919,6 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>研究科技</t>
@@ -956,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
@@ -979,7 +973,6 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>锻造基础金属工具与武器</t>
@@ -1006,7 +999,7 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>90</v>
@@ -1029,7 +1022,6 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>可锻造精良品质装备</t>
@@ -1061,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
         <v>120</v>
@@ -1084,7 +1076,6 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>可锻造稀有品质装备</t>
@@ -1116,7 +1107,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
         <v>180</v>
@@ -1139,7 +1130,6 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>大师级锻造台，可锻造传说品质装备</t>
@@ -1194,7 +1184,6 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>村子级别的低矮小墙，不能站人</t>
@@ -1253,7 +1242,6 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>标准城墙，上面可以站人</t>
@@ -1312,7 +1300,6 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>上面能放一堆器械的大墙</t>
@@ -1371,7 +1358,6 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>城墙上的门，允许己方通行，可关闭拒敌</t>
@@ -1430,7 +1416,6 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>城墙外侧的沟渠，减缓/阻挡敌方移动</t>
@@ -1489,7 +1474,6 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>储存建材，工人从此取货运往工地</t>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1480,6 +1480,55 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>stone_warehouse</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>石造仓库</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>120</v>
+      </c>
+      <c r="G20" t="n">
+        <v>80</v>
+      </c>
+      <c r="H20" t="n">
+        <v>220</v>
+      </c>
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="J20" t="n">
+        <v>650</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>厚石墙仓储建筑，储重物抗风雪</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1529,6 +1529,55 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>manor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>宅邸</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>150</v>
+      </c>
+      <c r="G21" t="n">
+        <v>120</v>
+      </c>
+      <c r="H21" t="n">
+        <v>160</v>
+      </c>
+      <c r="I21" t="n">
+        <v>80</v>
+      </c>
+      <c r="J21" t="n">
+        <v>700</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>两层半木悬挑宅邸，外梯上二层，镇上有头脸人家的住处</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stick-world/config/excel/建筑数据.xlsx
+++ b/stick-world/config/excel/建筑数据.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1578,6 +1578,104 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>timber_cottage</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>木骨民居</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90</v>
+      </c>
+      <c r="H22" t="n">
+        <v>70</v>
+      </c>
+      <c r="I22" t="n">
+        <v>20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>450</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>石基木骨的小民居，金茅草双坡顶，可进屋</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>grand_hall</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>议事厅</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>hall</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>200</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150</v>
+      </c>
+      <c r="H23" t="n">
+        <v>260</v>
+      </c>
+      <c r="I23" t="n">
+        <v>90</v>
+      </c>
+      <c r="J23" t="n">
+        <v>900</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>村镇议事大厅，石砌基层半木二层脊上钟楼（地标）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
